--- a/Lab03 - Data Acquisition/notebooks/task3_deliverables/scraped_data/task3_books.xlsx
+++ b/Lab03 - Data Acquisition/notebooks/task3_deliverables/scraped_data/task3_books.xlsx
@@ -429,17 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>availability</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>category</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>availability</t>
         </is>
       </c>
     </row>
@@ -452,16 +452,16 @@
       <c r="B2" t="n">
         <v>47.82</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -473,16 +473,16 @@
       <c r="B3" t="n">
         <v>19.63</v>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
       <c r="B4" t="n">
         <v>56.5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -515,16 +515,16 @@
       <c r="B5" t="n">
         <v>16.64</v>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -536,16 +536,16 @@
       <c r="B6" t="n">
         <v>44.1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
       <c r="B7" t="n">
         <v>54.21</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -578,16 +578,16 @@
       <c r="B8" t="n">
         <v>13.92</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -599,16 +599,16 @@
       <c r="B9" t="n">
         <v>10.69</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -620,16 +620,16 @@
       <c r="B10" t="n">
         <v>48.35</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -641,16 +641,16 @@
       <c r="B11" t="n">
         <v>16.73</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -662,16 +662,16 @@
       <c r="B12" t="n">
         <v>26.8</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -683,16 +683,16 @@
       <c r="B13" t="n">
         <v>54.36</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -704,16 +704,16 @@
       <c r="B14" t="n">
         <v>35.28</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -725,16 +725,16 @@
       <c r="B15" t="n">
         <v>11.84</v>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E15" t="b">
-        <v>1</v>
+      <c r="C15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -746,16 +746,16 @@
       <c r="B16" t="n">
         <v>59.48</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -767,16 +767,16 @@
       <c r="B17" t="n">
         <v>27.26</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -788,16 +788,16 @@
       <c r="B18" t="n">
         <v>13.71</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
         <v>3</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -809,16 +809,16 @@
       <c r="B19" t="n">
         <v>25.37</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -830,16 +830,16 @@
       <c r="B20" t="n">
         <v>52.3</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -851,16 +851,16 @@
       <c r="B21" t="n">
         <v>20.89</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -872,16 +872,16 @@
       <c r="B22" t="n">
         <v>24.8</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
         <v>4</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -893,16 +893,16 @@
       <c r="B23" t="n">
         <v>38.38</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -914,16 +914,16 @@
       <c r="B24" t="n">
         <v>23.05</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>5</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -935,16 +935,16 @@
       <c r="B25" t="n">
         <v>43.45</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -956,16 +956,16 @@
       <c r="B26" t="n">
         <v>19.21</v>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
+      <c r="C26" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -977,16 +977,16 @@
       <c r="B27" t="n">
         <v>25.4</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -998,16 +998,16 @@
       <c r="B28" t="n">
         <v>24.72</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>2</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1019,16 +1019,16 @@
       <c r="B29" t="n">
         <v>57.7</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>4</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1040,16 +1040,16 @@
       <c r="B30" t="n">
         <v>12.29</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1061,16 +1061,16 @@
       <c r="B31" t="n">
         <v>15.85</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
         <v>3</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1082,16 +1082,16 @@
       <c r="B32" t="n">
         <v>20.3</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
         <v>3</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1103,16 +1103,16 @@
       <c r="B33" t="n">
         <v>53.98</v>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Mystery</t>
-        </is>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
+      <c r="C33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1124,16 +1124,16 @@
       <c r="B34" t="n">
         <v>37.59</v>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C34" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E34" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1145,16 +1145,16 @@
       <c r="B35" t="n">
         <v>35.67</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
         <v>5</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1166,16 +1166,16 @@
       <c r="B36" t="n">
         <v>43.3</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
         <v>4</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E36" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1187,16 +1187,16 @@
       <c r="B37" t="n">
         <v>10.65</v>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C37" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E37" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1208,16 +1208,16 @@
       <c r="B38" t="n">
         <v>26.12</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
         <v>2</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E38" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1229,16 +1229,16 @@
       <c r="B39" t="n">
         <v>48.74</v>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C39" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E39" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1250,16 +1250,16 @@
       <c r="B40" t="n">
         <v>21.36</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
         <v>4</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E40" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1271,16 +1271,16 @@
       <c r="B41" t="n">
         <v>32.42</v>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C41" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E41" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1292,16 +1292,16 @@
       <c r="B42" t="n">
         <v>10.92</v>
       </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C42" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E42" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1313,16 +1313,16 @@
       <c r="B43" t="n">
         <v>19.07</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
         <v>4</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E43" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1334,16 +1334,16 @@
       <c r="B44" t="n">
         <v>33.26</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
         <v>2</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E44" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1355,16 +1355,16 @@
       <c r="B45" t="n">
         <v>54.86</v>
       </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E45" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1376,16 +1376,16 @@
       <c r="B46" t="n">
         <v>51.48</v>
       </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C46" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E46" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1397,16 +1397,16 @@
       <c r="B47" t="n">
         <v>44.18</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
         <v>2</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E47" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1418,16 +1418,16 @@
       <c r="B48" t="n">
         <v>36.26</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
         <v>2</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E48" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1439,16 +1439,16 @@
       <c r="B49" t="n">
         <v>34.96</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" t="b">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
         <v>4</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Science Fiction</t>
         </is>
-      </c>
-      <c r="E49" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1460,16 +1460,16 @@
       <c r="B50" t="n">
         <v>18.78</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" t="b">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
         <v>3</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1481,16 +1481,16 @@
       <c r="B51" t="n">
         <v>25.02</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
         <v>3</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E51" t="b">
-        <v>1</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1502,16 +1502,16 @@
       <c r="B52" t="n">
         <v>13.34</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" t="b">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
         <v>5</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E52" t="b">
-        <v>1</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1523,16 +1523,16 @@
       <c r="B53" t="n">
         <v>56.4</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" t="b">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
         <v>2</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E53" t="b">
-        <v>1</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1544,16 +1544,16 @@
       <c r="B54" t="n">
         <v>43.29</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" t="b">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
         <v>3</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E54" t="b">
-        <v>1</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1565,16 +1565,16 @@
       <c r="B55" t="n">
         <v>28.09</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" t="b">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
         <v>2</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E55" t="b">
-        <v>1</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1586,16 +1586,16 @@
       <c r="B56" t="n">
         <v>52.37</v>
       </c>
-      <c r="C56" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E56" t="b">
-        <v>1</v>
+      <c r="C56" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1607,16 +1607,16 @@
       <c r="B57" t="n">
         <v>35.07</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
         <v>3</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E57" t="b">
-        <v>1</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -1628,16 +1628,16 @@
       <c r="B58" t="n">
         <v>44.28</v>
       </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E58" t="b">
-        <v>1</v>
+      <c r="C58" t="b">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1649,16 +1649,16 @@
       <c r="B59" t="n">
         <v>42.98</v>
       </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E59" t="b">
-        <v>1</v>
+      <c r="C59" t="b">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1670,16 +1670,16 @@
       <c r="B60" t="n">
         <v>32.3</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
         <v>5</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E60" t="b">
-        <v>1</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1691,16 +1691,16 @@
       <c r="B61" t="n">
         <v>52.26</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
         <v>2</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E61" t="b">
-        <v>1</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1712,16 +1712,16 @@
       <c r="B62" t="n">
         <v>44.73</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" t="b">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
         <v>4</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E62" t="b">
-        <v>1</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1733,16 +1733,16 @@
       <c r="B63" t="n">
         <v>29.65</v>
       </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E63" t="b">
-        <v>1</v>
+      <c r="C63" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1754,16 +1754,16 @@
       <c r="B64" t="n">
         <v>37.51</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" t="b">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
         <v>5</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E64" t="b">
-        <v>1</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1775,16 +1775,16 @@
       <c r="B65" t="n">
         <v>56.02</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
         <v>4</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E65" t="b">
-        <v>1</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1796,16 +1796,16 @@
       <c r="B66" t="n">
         <v>38.73</v>
       </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E66" t="b">
-        <v>1</v>
+      <c r="C66" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1817,16 +1817,16 @@
       <c r="B67" t="n">
         <v>56.63</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
         <v>3</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E67" t="b">
-        <v>1</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -1838,16 +1838,16 @@
       <c r="B68" t="n">
         <v>39.61</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" t="b">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
         <v>5</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E68" t="b">
-        <v>1</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1859,16 +1859,16 @@
       <c r="B69" t="n">
         <v>12.16</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" t="b">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
         <v>5</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E69" t="b">
-        <v>1</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -1880,16 +1880,16 @@
       <c r="B70" t="n">
         <v>44.81</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" t="b">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
         <v>4</v>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E70" t="b">
-        <v>1</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -1901,16 +1901,16 @@
       <c r="B71" t="n">
         <v>57.74</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
         <v>4</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E71" t="b">
-        <v>1</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -1922,16 +1922,16 @@
       <c r="B72" t="n">
         <v>56</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" t="b">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
         <v>5</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E72" t="b">
-        <v>1</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -1943,16 +1943,16 @@
       <c r="B73" t="n">
         <v>45.51</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" t="b">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
         <v>3</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E73" t="b">
-        <v>1</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -1964,16 +1964,16 @@
       <c r="B74" t="n">
         <v>17.21</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" t="b">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
         <v>4</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E74" t="b">
-        <v>1</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -1985,16 +1985,16 @@
       <c r="B75" t="n">
         <v>52.11</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
         <v>2</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E75" t="b">
-        <v>1</v>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -2006,16 +2006,16 @@
       <c r="B76" t="n">
         <v>46.08</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" t="b">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
         <v>5</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E76" t="b">
-        <v>1</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -2027,16 +2027,16 @@
       <c r="B77" t="n">
         <v>49.45</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" t="b">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
         <v>5</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E77" t="b">
-        <v>1</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2048,16 +2048,16 @@
       <c r="B78" t="n">
         <v>31.63</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" t="b">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
         <v>4</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E78" t="b">
-        <v>1</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2069,16 +2069,16 @@
       <c r="B79" t="n">
         <v>48.75</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
         <v>5</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E79" t="b">
-        <v>1</v>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2090,16 +2090,16 @@
       <c r="B80" t="n">
         <v>14.74</v>
       </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E80" t="b">
-        <v>1</v>
+      <c r="C80" t="b">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2111,16 +2111,16 @@
       <c r="B81" t="n">
         <v>58.64</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" t="b">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
         <v>4</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E81" t="b">
-        <v>1</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -2132,16 +2132,16 @@
       <c r="B82" t="n">
         <v>24.72</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" t="b">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
         <v>2</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E82" t="b">
-        <v>1</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -2153,16 +2153,16 @@
       <c r="B83" t="n">
         <v>55.46</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" t="b">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
         <v>2</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E83" t="b">
-        <v>1</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -2174,16 +2174,16 @@
       <c r="B84" t="n">
         <v>44.07</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" t="b">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
         <v>4</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E84" t="b">
-        <v>1</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -2195,16 +2195,16 @@
       <c r="B85" t="n">
         <v>43.87</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" t="b">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
         <v>3</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E85" t="b">
-        <v>1</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2216,16 +2216,16 @@
       <c r="B86" t="n">
         <v>56.02</v>
       </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E86" t="b">
-        <v>1</v>
+      <c r="C86" t="b">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -2237,16 +2237,16 @@
       <c r="B87" t="n">
         <v>22.06</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" t="b">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
         <v>4</v>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E87" t="b">
-        <v>1</v>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -2258,16 +2258,16 @@
       <c r="B88" t="n">
         <v>31.22</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" t="b">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
         <v>2</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E88" t="b">
-        <v>1</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -2279,16 +2279,16 @@
       <c r="B89" t="n">
         <v>53.82</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" t="b">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
         <v>2</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E89" t="b">
-        <v>1</v>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -2300,16 +2300,16 @@
       <c r="B90" t="n">
         <v>36.25</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" t="b">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
         <v>3</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E90" t="b">
-        <v>1</v>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -2321,16 +2321,16 @@
       <c r="B91" t="n">
         <v>29.38</v>
       </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E91" t="b">
-        <v>1</v>
+      <c r="C91" t="b">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -2342,16 +2342,16 @@
       <c r="B92" t="n">
         <v>13.33</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" t="b">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
         <v>3</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E92" t="b">
-        <v>1</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -2363,16 +2363,16 @@
       <c r="B93" t="n">
         <v>21.72</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" t="b">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
         <v>4</v>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E93" t="b">
-        <v>1</v>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -2384,16 +2384,16 @@
       <c r="B94" t="n">
         <v>28.99</v>
       </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E94" t="b">
-        <v>1</v>
+      <c r="C94" t="b">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -2405,16 +2405,16 @@
       <c r="B95" t="n">
         <v>52.94</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" t="b">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
         <v>2</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E95" t="b">
-        <v>1</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2426,16 +2426,16 @@
       <c r="B96" t="n">
         <v>58.75</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" t="b">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
         <v>4</v>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Fantasy</t>
-        </is>
-      </c>
-      <c r="E96" t="b">
-        <v>1</v>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
       </c>
     </row>
   </sheetData>
